--- a/docs/CEF_Detailed_Budget_Table_FIXED.xlsx
+++ b/docs/CEF_Detailed_Budget_Table_FIXED.xlsx
@@ -571,10 +571,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Project Acronym: AETERNA-SCW  // Proposal ID: CEF-DIG-2026-SMART-CABLES-101538202</t>
-        </is>
-      </c>
-    </row>
+          <t>Project Acronym: AETERNA-SCW  // Proposal ID: CEF-DIG-2026-SMART-CABLES-101354145</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -596,13 +597,15 @@
           <t>Munich Institute (DE)</t>
         </is>
       </c>
-      <c r="E4" s="3">
-        <f>SUM(B4:D4)</f>
-        <v/>
-      </c>
-      <c r="F4" s="3">
-        <f>ROUND(E4*0.5, 2)</f>
-        <v/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Total Budget (€)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>EU Requested (50%) (€)</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -625,7 +628,7 @@
         <v/>
       </c>
       <c r="F5" s="7">
-        <f>ROUND(E5*0.5, 2)</f>
+        <f>E5*0.5</f>
         <v/>
       </c>
     </row>
@@ -649,7 +652,7 @@
         <v/>
       </c>
       <c r="F6" s="11">
-        <f>ROUND(E6*0.5, 2)</f>
+        <f>E6*0.5</f>
         <v/>
       </c>
     </row>
@@ -673,7 +676,7 @@
         <v/>
       </c>
       <c r="F7" s="7">
-        <f>ROUND(E7*0.5, 2)</f>
+        <f>E7*0.5</f>
         <v/>
       </c>
     </row>
@@ -697,7 +700,7 @@
         <v/>
       </c>
       <c r="F8" s="11">
-        <f>ROUND(E8*0.5, 2)</f>
+        <f>E8*0.5</f>
         <v/>
       </c>
     </row>
@@ -707,24 +710,21 @@
           <t>E. Direct Purchase: Other goods &amp; services</t>
         </is>
       </c>
-      <c r="B9" s="5">
-        <f>ROUND((B4+B6+B7+B8)*0.07, 2)</f>
-        <v/>
-      </c>
-      <c r="C9" s="5">
-        <f>ROUND((C4+C6+C7+C8)*0.07, 2)</f>
-        <v/>
-      </c>
-      <c r="D9" s="5">
-        <f>ROUND((D4+D6+D7+D8)*0.07, 2)</f>
-        <v/>
+      <c r="B9" s="5" t="n">
+        <v>443925.23</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>490186.92</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>105607.48</v>
       </c>
       <c r="E9" s="6">
         <f>SUM(B9:D9)</f>
         <v/>
       </c>
       <c r="F9" s="7">
-        <f>ROUND(E9*0.5, 2)</f>
+        <f>E9*0.5</f>
         <v/>
       </c>
     </row>
@@ -735,15 +735,15 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <f>ROUND(SUM(B4:B9), 2)</f>
+        <f>(B5+B7+B8+B9)*0.07</f>
         <v/>
       </c>
       <c r="C10" s="13">
-        <f>ROUND(SUM(C4:C9), 2)</f>
+        <f>(C5+C7+C8+C9)*0.07</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>ROUND(SUM(D4:D9), 2)</f>
+        <f>(D5+D7+D8+D9)*0.07</f>
         <v/>
       </c>
       <c r="E10" s="14">
@@ -751,7 +751,7 @@
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>ROUND(E10*0.5, 2)</f>
+        <f>E10*0.5</f>
         <v/>
       </c>
     </row>
@@ -762,23 +762,23 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>ROUND(B10*0.5, 2)</f>
+        <f>SUM(B5:B10)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>ROUND(C10*0.5, 2)</f>
+        <f>SUM(C5:C10)</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>ROUND(D10*0.5, 2)</f>
+        <f>SUM(D5:D10)</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>SUM(B11:D11)</f>
+        <f>SUM(E5:E10)</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>ROUND(E11*0.5, 2)</f>
+        <f>SUM(F5:F10)</f>
         <v/>
       </c>
     </row>
